--- a/GeoInput.xlsx
+++ b/GeoInput.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TRNSYS18\TRNLib\CallingPython-Cffi\Examples\trnsys-neighbourhood\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21F3E98-C457-4580-907B-5EEDFF429ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB44569-602E-4C5C-9D73-60340B9CAE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Borehole" sheetId="1" r:id="rId1"/>
@@ -573,7 +573,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B3" s="2">
         <v>6</v>
@@ -589,7 +589,7 @@
       </c>
       <c r="F3" s="2">
         <f t="shared" ref="F3:F5" si="0">A3*10*8760/1000</f>
-        <v>11388</v>
+        <v>10512</v>
       </c>
       <c r="G3" s="2">
         <v>2002</v>
@@ -621,7 +621,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="B5" s="2">
         <v>6</v>
@@ -637,7 +637,7 @@
       </c>
       <c r="F5" s="2">
         <f t="shared" si="0"/>
-        <v>11388</v>
+        <v>13140</v>
       </c>
       <c r="G5" s="2">
         <v>2004</v>
